--- a/Result/profitability/4739.xlsx
+++ b/Result/profitability/4739.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8387499999999999</v>
+        <v>1.04625</v>
       </c>
       <c r="N2" t="n">
-        <v>13.44875</v>
+        <v>13.61125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-1.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5912499999999999</v>
+        <v>0.82</v>
       </c>
       <c r="N3" t="n">
-        <v>11.4325</v>
+        <v>12.22375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6224999999999999</v>
+        <v>0.9012499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.3225</v>
+        <v>10.91125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7874999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>10.18875</v>
+        <v>10.9225</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.86</v>
+        <v>1.02125</v>
       </c>
       <c r="N6" t="n">
-        <v>10.2975</v>
+        <v>10.7375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8225</v>
+        <v>0.9450000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>9.65625</v>
+        <v>9.7675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0.84</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0.86125</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9300,6 +9300,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4739</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3140</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2644</v>
+      </c>
+      <c r="E71" t="n">
+        <v>496</v>
+      </c>
+      <c r="F71" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>378</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>12.05%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J71" t="n">
+        <v>376</v>
+      </c>
+      <c r="K71" t="n">
+        <v>248</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="N71" t="n">
+        <v>14.23875</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.3245033112582782</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-2.129999999999999</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.1187953151143335</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>32.33333333333334</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>5.870000000000001</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.5911379657603224</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
